--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8477-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8477-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE3B2600-4A0B-4D21-8A9A-BF037A192044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2C1EBD0-C39D-457D-B5DF-55D01590C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F77D0BF2-5CB2-420D-9AF2-EDE42669840D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DB1B1E11-9B6C-4528-B816-BCA5B284BFFB}"/>
   </bookViews>
   <sheets>
     <sheet name="8477-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1505,29 +1505,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65100B69-1FFF-4B92-9CB6-835F1E531B29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91BB741C-2A63-4A00-9360-9B1507605B65}">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.75" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1560,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1597,7 +1596,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1648,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1717,7 +1716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1789,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <v>2018</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="43"/>
       <c r="B12" s="44"/>
       <c r="C12" s="18" t="s">
@@ -2249,7 +2248,7 @@
       <c r="W12" s="50"/>
       <c r="X12" s="46"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="51">
         <v>2017</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="53"/>
       <c r="B14" s="54"/>
       <c r="C14" s="20" t="s">
@@ -2349,7 +2348,7 @@
       <c r="W14" s="60"/>
       <c r="X14" s="56"/>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2016</v>
       </c>
@@ -2421,7 +2420,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2015</v>
       </c>
@@ -2493,7 +2492,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2014</v>
       </c>
@@ -2565,7 +2564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
         <v>37</v>
       </c>
